--- a/Main Results.xlsx
+++ b/Main Results.xlsx
@@ -8,18 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krishna Nohwal\Desktop\TimelyDINO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B00FA208-ADE1-4D11-9BDE-63592B94F3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6A9763-581E-418F-A362-85821B1A2F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5FE3D1AE-251E-4BEC-B504-AD9EA38BBDCF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Main Results" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -33,6 +30,182 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Codex</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source not located; value retained from existing workbook, not fabricated</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>https://arxiv.org/abs/2304.13949</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Source not located; value retained from existing workbook, not fabricated</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>https://arxiv.org/abs/2204.08376</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Venue</t>
+  </si>
+  <si>
+    <t>CDFv1</t>
+  </si>
+  <si>
+    <t>CDFv2</t>
+  </si>
+  <si>
+    <t>DFD</t>
+  </si>
+  <si>
+    <t>DFDC</t>
+  </si>
+  <si>
+    <t>WDF</t>
+  </si>
+  <si>
+    <t>SBI</t>
+  </si>
+  <si>
+    <t>CVPR'22</t>
+  </si>
+  <si>
+    <t>LSDA</t>
+  </si>
+  <si>
+    <t>CVPR'24</t>
+  </si>
+  <si>
+    <t>UCF</t>
+  </si>
+  <si>
+    <t>ICCV'23</t>
+  </si>
+  <si>
+    <t>Effort</t>
+  </si>
+  <si>
+    <t>ICML'25</t>
+  </si>
+  <si>
+    <t>LAA-Net</t>
+  </si>
+  <si>
+    <t>DF0</t>
+  </si>
+  <si>
+    <t>KFD</t>
+  </si>
+  <si>
+    <t>ForAda</t>
+  </si>
+  <si>
+    <t>CVPR'25</t>
+  </si>
+  <si>
+    <t>ProDet</t>
+  </si>
+  <si>
+    <t>NIPS'24</t>
+  </si>
+  <si>
+    <t>UDD</t>
+  </si>
+  <si>
+    <t>AAAI'25</t>
+  </si>
+  <si>
+    <t>LVLM-DFD</t>
+  </si>
+  <si>
+    <t>RECCE</t>
+  </si>
+  <si>
+    <t>X2-DFD</t>
+  </si>
+  <si>
+    <t>NIPS'25</t>
+  </si>
+  <si>
+    <t>DFD-HR</t>
+  </si>
+  <si>
+    <t>CVPR'26</t>
+  </si>
+  <si>
+    <t>https://openaccess.thecvf.com/content/CVPR2026/papers/Sun_DFD-HR_Generalizable_Deepfake_Detection_via_Hierarchical_Routing_Learning_CVPR_2026_paper.pdf</t>
+  </si>
+  <si>
+    <t>ForensicsAdapter</t>
+  </si>
+  <si>
+    <t>97..3</t>
+  </si>
+  <si>
+    <t>QTFP</t>
+  </si>
+  <si>
+    <t>https://openaccess.thecvf.com/content/CVPR2026/papers/Wang_Beyond_CLS_Token_Query-Driven_Token-Level_Forgery_Purification_for_Generalizable_Deepfake_CVPR_2026_paper.pdf</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -66,8 +239,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,10 +580,402 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8863569-7399-46F7-8E52-2F21B683865F}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="62" customWidth="1"/>
+    <col min="4" max="8" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="2">
+        <v>90.94</v>
+      </c>
+      <c r="E2" s="2">
+        <v>92.6</v>
+      </c>
+      <c r="F2">
+        <v>90.1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>70.7</v>
+      </c>
+      <c r="H2" s="2">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="I2" s="2">
+        <v>87.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2">
+        <v>96.05</v>
+      </c>
+      <c r="E3" s="2">
+        <v>95.6</v>
+      </c>
+      <c r="F3" s="2">
+        <v>96.5</v>
+      </c>
+      <c r="G3" s="2">
+        <v>84.3</v>
+      </c>
+      <c r="H3" s="2">
+        <v>84.8</v>
+      </c>
+      <c r="I3" s="2">
+        <v>97.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2">
+        <v>97.62</v>
+      </c>
+      <c r="E4" s="2">
+        <v>94.71</v>
+      </c>
+      <c r="G4" s="2">
+        <v>79.12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="2">
+        <v>86.08</v>
+      </c>
+      <c r="E5" s="2">
+        <v>83.73</v>
+      </c>
+      <c r="F5" s="2">
+        <v>86.7</v>
+      </c>
+      <c r="G5" s="2">
+        <v>75.11</v>
+      </c>
+      <c r="H5" s="2">
+        <v>77.42</v>
+      </c>
+      <c r="I5" s="2">
+        <v>80.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2">
+        <v>86.08</v>
+      </c>
+      <c r="E6" s="2">
+        <v>95.7</v>
+      </c>
+      <c r="F6" s="2">
+        <v>97.2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>87.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="2">
+        <v>86.79</v>
+      </c>
+      <c r="E7" s="2">
+        <v>89.8</v>
+      </c>
+      <c r="F7" s="2">
+        <v>95.6</v>
+      </c>
+      <c r="G7" s="2">
+        <v>73.5</v>
+      </c>
+      <c r="H7" s="2">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="I7" s="2">
+        <v>89.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2">
+        <v>95.4</v>
+      </c>
+      <c r="F8" s="2">
+        <v>98.4</v>
+      </c>
+      <c r="H8" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="2">
+        <v>93.44</v>
+      </c>
+      <c r="E9" s="2">
+        <v>93.18</v>
+      </c>
+      <c r="F9" s="2">
+        <v>82.7</v>
+      </c>
+      <c r="G9" s="2">
+        <v>74.47</v>
+      </c>
+      <c r="H9" s="2">
+        <v>70.3</v>
+      </c>
+      <c r="I9" s="2">
+        <v>89.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10">
+        <v>93.1</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2">
+        <v>95.5</v>
+      </c>
+      <c r="G10" s="2">
+        <v>81.209999999999994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11">
+        <v>97.62</v>
+      </c>
+      <c r="E11" s="2">
+        <v>94.71</v>
+      </c>
+      <c r="G11" s="2">
+        <v>91.81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12">
+        <v>81.8</v>
+      </c>
+      <c r="E12" s="2">
+        <v>82.3</v>
+      </c>
+      <c r="F12" s="2">
+        <v>89.1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>69.599999999999994</v>
+      </c>
+      <c r="H12" s="2">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="I12">
+        <v>78.400000000000006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13">
+        <v>95.7</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2">
+        <v>96.1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14">
+        <v>96</v>
+      </c>
+      <c r="F14" s="2">
+        <v>98</v>
+      </c>
+      <c r="G14" s="2">
+        <v>86.5</v>
+      </c>
+      <c r="H14">
+        <v>90.7</v>
+      </c>
+      <c r="I14">
+        <v>99.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="2">
+        <v>95.6</v>
+      </c>
+      <c r="F15" s="2">
+        <v>96</v>
+      </c>
+      <c r="G15" s="2">
+        <v>86.9</v>
+      </c>
+      <c r="H15" s="2">
+        <v>89</v>
+      </c>
+      <c r="I15" s="2">
+        <v>97.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16">
+        <v>98</v>
+      </c>
+      <c r="E16" s="2">
+        <v>96</v>
+      </c>
+      <c r="F16" s="2">
+        <v>97.5</v>
+      </c>
+      <c r="G16" s="2">
+        <v>86.9</v>
+      </c>
+      <c r="H16" s="2">
+        <v>91.7</v>
+      </c>
+      <c r="I16" s="2">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D17">
+        <v>99.53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I9">
+    <sortCondition descending="1" ref="B1:B9"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Main Results.xlsx
+++ b/Main Results.xlsx
@@ -2,33 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krishna Nohwal\Desktop\TimelyDINO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6A9763-581E-418F-A362-85821B1A2F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D7DC2B-3652-4C11-B2C4-D2176F427028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Results" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -38,57 +25,49 @@
     <author>Codex</author>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Aptos Narrow"/>
-            <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t>Source not located; value retained from existing workbook, not fabricated</t>
         </r>
       </text>
     </comment>
-    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Aptos Narrow"/>
-            <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t>https://arxiv.org/abs/2304.13949</t>
         </r>
       </text>
     </comment>
-    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Aptos Narrow"/>
-            <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t>Source not located; value retained from existing workbook, not fabricated</t>
         </r>
       </text>
     </comment>
-    <comment ref="C9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Aptos Narrow"/>
-            <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
           <t>https://arxiv.org/abs/2204.08376</t>
         </r>
@@ -99,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
   <si>
     <t>Method</t>
   </si>
@@ -122,22 +101,37 @@
     <t>WDF</t>
   </si>
   <si>
+    <t>DF0</t>
+  </si>
+  <si>
     <t>SBI</t>
   </si>
   <si>
     <t>CVPR'22</t>
   </si>
   <si>
+    <t>RECCE</t>
+  </si>
+  <si>
+    <t>UCF</t>
+  </si>
+  <si>
+    <t>ICCV'23</t>
+  </si>
+  <si>
+    <t>ProDet</t>
+  </si>
+  <si>
+    <t>NIPS'24</t>
+  </si>
+  <si>
     <t>LSDA</t>
   </si>
   <si>
     <t>CVPR'24</t>
   </si>
   <si>
-    <t>UCF</t>
-  </si>
-  <si>
-    <t>ICCV'23</t>
+    <t>LAA-Net</t>
   </si>
   <si>
     <t>Effort</t>
@@ -146,12 +140,6 @@
     <t>ICML'25</t>
   </si>
   <si>
-    <t>LAA-Net</t>
-  </si>
-  <si>
-    <t>DF0</t>
-  </si>
-  <si>
     <t>KFD</t>
   </si>
   <si>
@@ -161,12 +149,6 @@
     <t>CVPR'25</t>
   </si>
   <si>
-    <t>ProDet</t>
-  </si>
-  <si>
-    <t>NIPS'24</t>
-  </si>
-  <si>
     <t>UDD</t>
   </si>
   <si>
@@ -176,34 +158,37 @@
     <t>LVLM-DFD</t>
   </si>
   <si>
-    <t>RECCE</t>
-  </si>
-  <si>
     <t>X2-DFD</t>
   </si>
   <si>
     <t>NIPS'25</t>
   </si>
   <si>
+    <t>ForensicsAdapter</t>
+  </si>
+  <si>
+    <t>97..3</t>
+  </si>
+  <si>
     <t>DFD-HR</t>
   </si>
   <si>
     <t>CVPR'26</t>
   </si>
   <si>
+    <t>QTFP</t>
+  </si>
+  <si>
     <t>https://openaccess.thecvf.com/content/CVPR2026/papers/Sun_DFD-HR_Generalizable_Deepfake_Detection_via_Hierarchical_Routing_Learning_CVPR_2026_paper.pdf</t>
   </si>
   <si>
-    <t>ForensicsAdapter</t>
-  </si>
-  <si>
-    <t>97..3</t>
-  </si>
-  <si>
-    <t>QTFP</t>
-  </si>
-  <si>
     <t>https://openaccess.thecvf.com/content/CVPR2026/papers/Wang_Beyond_CLS_Token_Query-Driven_Token-Level_Forgery_Purification_for_Generalizable_Deepfake_CVPR_2026_paper.pdf</t>
+  </si>
+  <si>
+    <t>Ours</t>
+  </si>
+  <si>
+    <t>Avg</t>
   </si>
 </sst>
 </file>
@@ -215,8 +200,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -307,108 +290,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -420,23 +309,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -446,23 +335,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -470,26 +359,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -524,17 +410,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -549,39 +435,14 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -590,7 +451,7 @@
     <col min="4" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -614,260 +475,272 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2">
+        <v>93.44</v>
+      </c>
+      <c r="E2" s="2">
+        <v>93.18</v>
+      </c>
+      <c r="F2">
+        <v>82.7</v>
+      </c>
+      <c r="G2" s="2">
+        <v>74.47</v>
+      </c>
+      <c r="H2" s="2">
+        <v>70.3</v>
+      </c>
+      <c r="I2" s="2">
+        <v>89.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>81.8</v>
+      </c>
+      <c r="E3" s="2">
+        <v>82.3</v>
+      </c>
+      <c r="F3" s="2">
+        <v>89.1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>69.599999999999994</v>
+      </c>
+      <c r="H3" s="2">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="I3" s="2">
+        <v>78.400000000000006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="2">
+        <v>86.08</v>
+      </c>
+      <c r="E4" s="2">
+        <v>83.73</v>
+      </c>
+      <c r="F4" s="2">
+        <v>86.7</v>
+      </c>
+      <c r="G4" s="2">
+        <v>75.11</v>
+      </c>
+      <c r="H4" s="2">
+        <v>77.42</v>
+      </c>
+      <c r="I4" s="2">
+        <v>80.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2">
+        <v>90.94</v>
+      </c>
+      <c r="E5" s="2">
+        <v>92.6</v>
+      </c>
+      <c r="F5">
+        <v>90.1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>70.7</v>
+      </c>
+      <c r="H5">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="I5">
+        <v>87.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="C6" s="1"/>
+      <c r="D6" s="2">
+        <v>86.79</v>
+      </c>
+      <c r="E6" s="2">
+        <v>89.8</v>
+      </c>
+      <c r="F6" s="2">
+        <v>95.6</v>
+      </c>
+      <c r="G6" s="2">
+        <v>73.5</v>
+      </c>
+      <c r="H6" s="2">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="I6" s="2">
+        <v>89.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2">
+        <v>95.4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>98.4</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="2">
+        <v>96.05</v>
+      </c>
+      <c r="E8" s="2">
+        <v>95.6</v>
+      </c>
+      <c r="F8" s="2">
+        <v>96.5</v>
+      </c>
+      <c r="G8" s="2">
+        <v>84.3</v>
+      </c>
+      <c r="H8" s="2">
+        <v>84.8</v>
+      </c>
+      <c r="I8" s="2">
+        <v>97.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9">
+        <v>97.62</v>
+      </c>
+      <c r="E9" s="2">
+        <v>94.71</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9">
+        <v>79.12</v>
+      </c>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2">
-        <v>90.94</v>
-      </c>
-      <c r="E2" s="2">
-        <v>92.6</v>
-      </c>
-      <c r="F2">
-        <v>90.1</v>
-      </c>
-      <c r="G2" s="2">
-        <v>70.7</v>
-      </c>
-      <c r="H2" s="2">
-        <v>78.099999999999994</v>
-      </c>
-      <c r="I2" s="2">
-        <v>87.9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2">
-        <v>96.05</v>
-      </c>
-      <c r="E3" s="2">
-        <v>95.6</v>
-      </c>
-      <c r="F3" s="2">
-        <v>96.5</v>
-      </c>
-      <c r="G3" s="2">
-        <v>84.3</v>
-      </c>
-      <c r="H3" s="2">
-        <v>84.8</v>
-      </c>
-      <c r="I3" s="2">
-        <v>97.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="2">
-        <v>97.62</v>
-      </c>
-      <c r="E4" s="2">
-        <v>94.71</v>
-      </c>
-      <c r="G4" s="2">
-        <v>79.12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="2">
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="2">
         <v>86.08</v>
       </c>
-      <c r="E5" s="2">
-        <v>83.73</v>
-      </c>
-      <c r="F5" s="2">
-        <v>86.7</v>
-      </c>
-      <c r="G5" s="2">
-        <v>75.11</v>
-      </c>
-      <c r="H5" s="2">
-        <v>77.42</v>
-      </c>
-      <c r="I5" s="2">
-        <v>80.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="2">
-        <v>86.08</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="E10" s="2">
         <v>95.7</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F10" s="2">
         <v>97.2</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G10" s="2">
         <v>87.3</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="2">
-        <v>86.79</v>
-      </c>
-      <c r="E7" s="2">
-        <v>89.8</v>
-      </c>
-      <c r="F7" s="2">
-        <v>95.6</v>
-      </c>
-      <c r="G7" s="2">
-        <v>73.5</v>
-      </c>
-      <c r="H7" s="2">
-        <v>75.599999999999994</v>
-      </c>
-      <c r="I7" s="2">
-        <v>89.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2">
-        <v>95.4</v>
-      </c>
-      <c r="F8" s="2">
-        <v>98.4</v>
-      </c>
-      <c r="H8" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="2">
-        <v>93.44</v>
-      </c>
-      <c r="E9" s="2">
-        <v>93.18</v>
-      </c>
-      <c r="F9" s="2">
-        <v>82.7</v>
-      </c>
-      <c r="G9" s="2">
-        <v>74.47</v>
-      </c>
-      <c r="H9" s="2">
-        <v>70.3</v>
-      </c>
-      <c r="I9" s="2">
-        <v>89.9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D10">
+      <c r="B11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11">
         <v>93.1</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2">
+      <c r="E11" s="2"/>
+      <c r="F11" s="2">
         <v>95.5</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G11" s="2">
         <v>81.209999999999994</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11">
-        <v>97.62</v>
-      </c>
-      <c r="E11" s="2">
-        <v>94.71</v>
-      </c>
-      <c r="G11" s="2">
-        <v>91.81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="D12">
-        <v>81.8</v>
+        <v>97.62</v>
       </c>
       <c r="E12" s="2">
-        <v>82.3</v>
-      </c>
-      <c r="F12" s="2">
-        <v>89.1</v>
+        <v>94.71</v>
       </c>
       <c r="G12" s="2">
-        <v>69.599999999999994</v>
-      </c>
-      <c r="H12" s="2">
-        <v>75.599999999999994</v>
-      </c>
-      <c r="I12">
-        <v>78.400000000000006</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>91.81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>27</v>
       </c>
       <c r="D13">
@@ -880,62 +753,63 @@
       <c r="G13" s="2">
         <v>86</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" t="s">
         <v>29</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
+        <v>95.6</v>
+      </c>
+      <c r="F14" s="2">
         <v>96</v>
       </c>
-      <c r="F14" s="2">
+      <c r="G14" s="2">
+        <v>86.9</v>
+      </c>
+      <c r="H14">
+        <v>89</v>
+      </c>
+      <c r="I14">
+        <v>97.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15">
+        <v>96</v>
+      </c>
+      <c r="F15" s="2">
         <v>98</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G15" s="2">
         <v>86.5</v>
       </c>
-      <c r="H14">
+      <c r="H15">
         <v>90.7</v>
       </c>
-      <c r="I14">
+      <c r="I15">
         <v>99.7</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="2">
-        <v>95.6</v>
-      </c>
-      <c r="F15" s="2">
-        <v>96</v>
-      </c>
-      <c r="G15" s="2">
-        <v>86.9</v>
-      </c>
-      <c r="H15" s="2">
-        <v>89</v>
-      </c>
-      <c r="I15" s="2">
-        <v>97.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="D16">
         <v>98</v>
@@ -957,13 +831,16 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="D17">
         <v>99.53</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -972,9 +849,6 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I9">
-    <sortCondition descending="1" ref="B1:B9"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/Main Results.xlsx
+++ b/Main Results.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krishna Nohwal\Desktop\TimelyDINO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D7DC2B-3652-4C11-B2C4-D2176F427028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428E713F-0C80-4647-8507-4B2E53BE42AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Results" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -78,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>Method</t>
   </si>
@@ -90,12 +103,6 @@
   </si>
   <si>
     <t>CDFv2</t>
-  </si>
-  <si>
-    <t>DFD</t>
-  </si>
-  <si>
-    <t>DFDC</t>
   </si>
   <si>
     <t>WDF</t>
@@ -195,10 +202,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
@@ -219,10 +232,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -230,8 +244,10 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -465,28 +481,24 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2">
         <v>93.44</v>
@@ -494,12 +506,7 @@
       <c r="E2" s="2">
         <v>93.18</v>
       </c>
-      <c r="F2">
-        <v>82.7</v>
-      </c>
-      <c r="G2" s="2">
-        <v>74.47</v>
-      </c>
+      <c r="G2" s="2"/>
       <c r="H2" s="2">
         <v>70.3</v>
       </c>
@@ -509,10 +516,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>81.8</v>
@@ -520,12 +527,8 @@
       <c r="E3" s="2">
         <v>82.3</v>
       </c>
-      <c r="F3" s="2">
-        <v>89.1</v>
-      </c>
-      <c r="G3" s="2">
-        <v>69.599999999999994</v>
-      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
       <c r="H3" s="2">
         <v>75.599999999999994</v>
       </c>
@@ -535,10 +538,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="2">
@@ -547,12 +550,8 @@
       <c r="E4" s="2">
         <v>83.73</v>
       </c>
-      <c r="F4" s="2">
-        <v>86.7</v>
-      </c>
-      <c r="G4" s="2">
-        <v>75.11</v>
-      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
       <c r="H4" s="2">
         <v>77.42</v>
       </c>
@@ -562,10 +561,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2">
         <v>90.94</v>
@@ -573,12 +572,7 @@
       <c r="E5" s="2">
         <v>92.6</v>
       </c>
-      <c r="F5">
-        <v>90.1</v>
-      </c>
-      <c r="G5" s="2">
-        <v>70.7</v>
-      </c>
+      <c r="G5" s="2"/>
       <c r="H5">
         <v>78.099999999999994</v>
       </c>
@@ -588,10 +582,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="2">
@@ -600,12 +594,8 @@
       <c r="E6" s="2">
         <v>89.8</v>
       </c>
-      <c r="F6" s="2">
-        <v>95.6</v>
-      </c>
-      <c r="G6" s="2">
-        <v>73.5</v>
-      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
       <c r="H6" s="2">
         <v>75.599999999999994</v>
       </c>
@@ -615,18 +605,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2">
         <v>95.4</v>
       </c>
-      <c r="F7" s="2">
-        <v>98.4</v>
-      </c>
+      <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7">
         <v>80</v>
@@ -634,10 +622,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="2">
@@ -646,12 +634,8 @@
       <c r="E8" s="2">
         <v>95.6</v>
       </c>
-      <c r="F8" s="2">
-        <v>96.5</v>
-      </c>
-      <c r="G8" s="2">
-        <v>84.3</v>
-      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
       <c r="H8" s="2">
         <v>84.8</v>
       </c>
@@ -661,10 +645,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D9">
         <v>97.62</v>
@@ -673,17 +657,14 @@
         <v>94.71</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9">
-        <v>79.12</v>
-      </c>
       <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2">
@@ -692,39 +673,31 @@
       <c r="E10" s="2">
         <v>95.7</v>
       </c>
-      <c r="F10" s="2">
-        <v>97.2</v>
-      </c>
-      <c r="G10" s="2">
-        <v>87.3</v>
-      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>93.1</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="2">
-        <v>95.5</v>
-      </c>
-      <c r="G11" s="2">
-        <v>81.209999999999994</v>
-      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D12">
         <v>97.62</v>
@@ -732,48 +705,38 @@
       <c r="E12" s="2">
         <v>94.71</v>
       </c>
-      <c r="G12" s="2">
-        <v>91.81</v>
-      </c>
+      <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D13">
         <v>95.7</v>
       </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="2">
-        <v>96.1</v>
-      </c>
-      <c r="G13" s="2">
-        <v>86</v>
-      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E14" s="2">
         <v>95.6</v>
       </c>
-      <c r="F14" s="2">
-        <v>96</v>
-      </c>
-      <c r="G14" s="2">
-        <v>86.9</v>
-      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
       <c r="H14">
         <v>89</v>
       </c>
@@ -783,20 +746,16 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E15">
         <v>96</v>
       </c>
-      <c r="F15" s="2">
-        <v>98</v>
-      </c>
-      <c r="G15" s="2">
-        <v>86.5</v>
-      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
       <c r="H15">
         <v>90.7</v>
       </c>
@@ -806,10 +765,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D16">
         <v>98</v>
@@ -817,12 +776,8 @@
       <c r="E16" s="2">
         <v>96</v>
       </c>
-      <c r="F16" s="2">
-        <v>97.5</v>
-      </c>
-      <c r="G16" s="2">
-        <v>86.9</v>
-      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
       <c r="H16" s="2">
         <v>91.7</v>
       </c>
@@ -830,26 +785,39 @@
         <v>99.2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>99.53</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>34</v>
+      <c r="E17" s="2">
+        <v>98.28</v>
+      </c>
+      <c r="H17">
+        <v>92.9</v>
+      </c>
+      <c r="I17">
+        <v>99.86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A19" r:id="rId1" xr:uid="{C2987F79-32EC-4CDC-80C3-B88FBE9172B5}"/>
+    <hyperlink ref="A20" r:id="rId2" xr:uid="{C044A410-F518-45BB-9CE7-5E115E8BB0AF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>